--- a/artfynd/A 26531-2025 artfynd.xlsx
+++ b/artfynd/A 26531-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017088</v>
       </c>
       <c r="B2" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26531-2025 artfynd.xlsx
+++ b/artfynd/A 26531-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017088</v>
       </c>
       <c r="B2" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26531-2025 artfynd.xlsx
+++ b/artfynd/A 26531-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017088</v>
       </c>
       <c r="B2" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26531-2025 artfynd.xlsx
+++ b/artfynd/A 26531-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017088</v>
       </c>
       <c r="B2" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26531-2025 artfynd.xlsx
+++ b/artfynd/A 26531-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017088</v>
       </c>
       <c r="B2" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26531-2025 artfynd.xlsx
+++ b/artfynd/A 26531-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017088</v>
       </c>
       <c r="B2" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
